--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/GUARDA PÓ BENGALA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/GUARDA PÓ BENGALA.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG TRILHA CG 1995 A 1999/ TITAN 2000 KS/ FAN125 2005 A 2008/ FAN150 2010 A 2015/ TITAN150 2004 A 2015/ TITAN160 2016 A 2021</t>
+          <t>GUARDA PÓ BENGALA TRILHA CG 1995 A 1999/ TITAN 2000 KS/ FAN125 2005 A 2008/ FAN150 2010 A 2015/ TITAN150 2004 A 2015/ TITAN160 2016 A 2021</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG EMBUS FAZER150 2014/ FACTOR150-125I</t>
+          <t>GUARDA PÓ BENGALA EMBUS FAZER150 2014/ FACTOR150-125I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -482,7 +482,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -495,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG EMBUS BROS NXR150-160/ XRE190</t>
+          <t>GUARDA PÓ BENGALA EMBUS BROS NXR150-160/ XRE190</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUARDA PÓ BENG EMBUS TWISTER CBX250/ CB300R/ CB250F </t>
+          <t xml:space="preserve">GUARDA PÓ BENGALA EMBUS TWISTER CBX250/ CB300R/ CB250F </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -528,7 +532,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +549,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG CROSSER XTZ150 201064</t>
+          <t>GUARDA PÓ BENGALA CROSSER XTZ150 201064</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -549,7 +557,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +574,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG TRILHA TITAN FAN150-160/ PCX150 2019/ BROS NXR125-150-160</t>
+          <t>GUARDA PÓ BENGALA TRILHA TITAN FAN150-160/ PCX150 2019/ BROS NXR125-150-160</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -570,7 +582,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,7 +599,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GUARDA PÓ  BENG IRON YBR125/ YES125/ KATANA125 176235</t>
+          <t>GUARDA PÓ  BENGALA IRON YBR125/ YES125/ KATANA125 176235</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -591,7 +607,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -604,7 +624,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG (PAR) CONTROSEALS TWISTER/ CB300/ FAZER250/ CBX750 6651GP</t>
+          <t>GUARDA PÓ BENGALA (PAR) CONTROSEALS TWISTER/ CB300/ FAZER250/ CBX750 6651GP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -612,7 +632,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG (PAR) VEDAMTORS CG125/ BZ/ POP/ WEB100/ DAF ZIG</t>
+          <t>GUARDA PÓ BENGALA (PAR) VEDAMTORS CG125/ BZ/ POP/ WEB100/ DAF ZIG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -633,7 +657,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,7 +674,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG (PAR) VEDA+ CG125 309</t>
+          <t>GUARDA PÓ BENGALA (PAR) VEDA+ CG125 309</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -656,7 +684,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -671,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG (PAR) EMBUS FAN TITAN150-160/ BROS NXR125-150-160/ XRE190</t>
+          <t>GUARDA PÓ BENGALA (PAR) EMBUS FAN TITAN150-160/ BROS NXR125-150-160/ XRE190</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -679,7 +707,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -692,7 +724,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GUARDA PÓ BENG (PAR) MOTOBOR+ FALCON/ CB600</t>
+          <t>GUARDA PÓ BENGALA (PAR) MOTOBOR+ FALCON/ CB600</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -700,7 +732,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/GUARDA PÓ BENGALA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/GUARDA PÓ BENGALA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -730,11 +670,6 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
     </row>
